--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193901</v>
+        <v>120193935</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450966</v>
+        <v>451016</v>
       </c>
       <c r="R2" t="n">
-        <v>6975936</v>
+        <v>6976094</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +762,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,22 +783,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193947</v>
+        <v>120193901</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,36 +832,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451001</v>
+        <v>450966</v>
       </c>
       <c r="R3" t="n">
-        <v>6976090</v>
+        <v>6975936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193913</v>
+        <v>120193961</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>77910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,26 +968,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450990</v>
+        <v>451013</v>
       </c>
       <c r="R4" t="n">
-        <v>6975968</v>
+        <v>6976185</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1055,22 +1055,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193961</v>
+        <v>120193883</v>
       </c>
       <c r="B5" t="n">
-        <v>77910</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,26 +1104,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451013</v>
+        <v>450948</v>
       </c>
       <c r="R5" t="n">
-        <v>6976185</v>
+        <v>6975913</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193935</v>
+        <v>120193913</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451016</v>
+        <v>450990</v>
       </c>
       <c r="R6" t="n">
-        <v>6976094</v>
+        <v>6975968</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,11 +1311,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1332,12 +1327,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1347,7 +1342,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193942</v>
+        <v>120193923</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>77910</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,36 +1376,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1419,13 +1409,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451001</v>
+        <v>450990</v>
       </c>
       <c r="R7" t="n">
-        <v>6976090</v>
+        <v>6975968</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1457,11 +1447,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1478,22 +1463,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1511,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193883</v>
+        <v>120193947</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,31 +1512,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1560,13 +1550,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450948</v>
+        <v>451001</v>
       </c>
       <c r="R8" t="n">
-        <v>6975913</v>
+        <v>6976090</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1624,12 +1614,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1647,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193923</v>
+        <v>120193942</v>
       </c>
       <c r="B9" t="n">
-        <v>77910</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,31 +1653,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1696,13 +1691,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R9" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,6 +1729,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1750,22 +1750,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1780,6 +1780,924 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120222147</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>450759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6976733</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120222151</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>450762</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6976737</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120222148</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>450803</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6976732</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120222156</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>450980</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6976531</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120222155</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>450928</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6976454</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120222157</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>450970</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6976524</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120222152</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>450724</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6976511</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120222146</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90905</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>450758</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6976724</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120222153</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Marntallsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>450925</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6976466</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2699,6 +2699,2116 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120336056</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>450831</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6976781</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120336060</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>450791</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6976761</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120336059</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>450821</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6976771</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120336053</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>450750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6976700</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120336062</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>450866</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6976496</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120336064</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>450930</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6976470</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120336169</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>450959</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6976237</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120336184</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>450866</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6976252</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120336055</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>450841</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6976771</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120336640</v>
+      </c>
+      <c r="B28" t="n">
+        <v>86895</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>510</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>450821</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6976791</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120336172</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>450959</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6976237</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120336181</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>450874</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6976230</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120336052</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>450710</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6976591</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120336065</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>450976</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6976536</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120336058</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>450840</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6976766</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120336063</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>450895</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6976431</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120336054</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78624</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>864</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>450821</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6976791</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120336051</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>450701</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6976531</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120336061</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>450820</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6976610</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120336176</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>450917</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6976181</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193935</v>
+        <v>120193947</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451016</v>
+        <v>451001</v>
       </c>
       <c r="R2" t="n">
-        <v>6976094</v>
+        <v>6976090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +767,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,22 +783,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193901</v>
+        <v>120193935</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,26 +832,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450966</v>
+        <v>451016</v>
       </c>
       <c r="R3" t="n">
-        <v>6975936</v>
+        <v>6976094</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,6 +903,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -919,22 +924,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -952,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193961</v>
+        <v>120193901</v>
       </c>
       <c r="B4" t="n">
-        <v>77910</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,26 +973,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451013</v>
+        <v>450966</v>
       </c>
       <c r="R4" t="n">
-        <v>6976185</v>
+        <v>6975936</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1055,22 +1060,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193883</v>
+        <v>120193942</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,31 +1109,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1137,13 +1147,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450948</v>
+        <v>451001</v>
       </c>
       <c r="R5" t="n">
-        <v>6975913</v>
+        <v>6976090</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,6 +1185,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1201,12 +1216,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1224,10 +1239,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193913</v>
+        <v>120193883</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,7 +1274,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1273,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450990</v>
+        <v>450948</v>
       </c>
       <c r="R6" t="n">
-        <v>6975968</v>
+        <v>6975913</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1360,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193923</v>
+        <v>120193913</v>
       </c>
       <c r="B7" t="n">
-        <v>77910</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,26 +1391,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1463,22 +1478,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193947</v>
+        <v>120193961</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>77926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,36 +1527,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1550,13 +1560,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451001</v>
+        <v>451013</v>
       </c>
       <c r="R8" t="n">
-        <v>6976090</v>
+        <v>6976185</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1604,22 +1614,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1637,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193942</v>
+        <v>120193923</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>77926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1653,36 +1663,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1691,13 +1696,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451001</v>
+        <v>450990</v>
       </c>
       <c r="R9" t="n">
-        <v>6976090</v>
+        <v>6975968</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1729,11 +1734,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1750,22 +1750,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222147</v>
+        <v>120222153</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450759</v>
+        <v>450925</v>
       </c>
       <c r="R10" t="n">
-        <v>6976733</v>
+        <v>6976466</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222151</v>
+        <v>120222155</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450762</v>
+        <v>450928</v>
       </c>
       <c r="R11" t="n">
-        <v>6976737</v>
+        <v>6976454</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222148</v>
+        <v>120222152</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450803</v>
+        <v>450724</v>
       </c>
       <c r="R12" t="n">
-        <v>6976732</v>
+        <v>6976511</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222156</v>
+        <v>120222148</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450980</v>
+        <v>450803</v>
       </c>
       <c r="R13" t="n">
-        <v>6976531</v>
+        <v>6976732</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222155</v>
+        <v>120222147</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450928</v>
+        <v>450759</v>
       </c>
       <c r="R14" t="n">
-        <v>6976454</v>
+        <v>6976733</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222157</v>
+        <v>120222156</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450970</v>
+        <v>450980</v>
       </c>
       <c r="R15" t="n">
-        <v>6976524</v>
+        <v>6976531</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222152</v>
+        <v>120222146</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>90923</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,25 +2407,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450724</v>
+        <v>450758</v>
       </c>
       <c r="R16" t="n">
-        <v>6976511</v>
+        <v>6976724</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222146</v>
+        <v>120222157</v>
       </c>
       <c r="B17" t="n">
-        <v>90905</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450758</v>
+        <v>450970</v>
       </c>
       <c r="R17" t="n">
-        <v>6976724</v>
+        <v>6976524</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222153</v>
+        <v>120222151</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450925</v>
+        <v>450762</v>
       </c>
       <c r="R18" t="n">
-        <v>6976466</v>
+        <v>6976737</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336056</v>
+        <v>120336176</v>
       </c>
       <c r="B19" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,25 +2713,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450831</v>
+        <v>450917</v>
       </c>
       <c r="R19" t="n">
-        <v>6976781</v>
+        <v>6976181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,11 +2777,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336060</v>
+        <v>120336169</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,21 +2819,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450791</v>
+        <v>450959</v>
       </c>
       <c r="R20" t="n">
-        <v>6976761</v>
+        <v>6976237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2884,11 +2879,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336059</v>
+        <v>120336063</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2921,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450821</v>
+        <v>450895</v>
       </c>
       <c r="R21" t="n">
-        <v>6976771</v>
+        <v>6976431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,10 +3012,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336053</v>
+        <v>120336184</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3034,20 +3024,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3062,13 +3052,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450750</v>
+        <v>450866</v>
       </c>
       <c r="R22" t="n">
-        <v>6976700</v>
+        <v>6976252</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3098,11 +3088,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3129,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336062</v>
+        <v>120336181</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3130,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,13 +3154,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450866</v>
+        <v>450874</v>
       </c>
       <c r="R23" t="n">
-        <v>6976496</v>
+        <v>6976230</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3205,11 +3190,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,10 +3216,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336064</v>
+        <v>120336061</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,21 +3232,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3276,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450930</v>
+        <v>450820</v>
       </c>
       <c r="R24" t="n">
-        <v>6976470</v>
+        <v>6976610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3343,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336169</v>
+        <v>120336062</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3359,21 +3339,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3383,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450959</v>
+        <v>450866</v>
       </c>
       <c r="R25" t="n">
-        <v>6976237</v>
+        <v>6976496</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,6 +3399,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336184</v>
+        <v>120336051</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,21 +3446,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3485,13 +3470,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450866</v>
+        <v>450701</v>
       </c>
       <c r="R26" t="n">
-        <v>6976252</v>
+        <v>6976531</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,6 +3506,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3537,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336055</v>
+        <v>120336058</v>
       </c>
       <c r="B27" t="n">
-        <v>79659</v>
+        <v>90594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3559,25 +3549,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3587,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450841</v>
+        <v>450840</v>
       </c>
       <c r="R27" t="n">
-        <v>6976771</v>
+        <v>6976766</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336640</v>
+        <v>120336055</v>
       </c>
       <c r="B28" t="n">
-        <v>86895</v>
+        <v>79659</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3666,25 +3656,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3684,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450821</v>
+        <v>450841</v>
       </c>
       <c r="R28" t="n">
-        <v>6976791</v>
+        <v>6976771</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3730,6 +3720,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3756,10 +3751,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336172</v>
+        <v>120336065</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,21 +3767,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450959</v>
+        <v>450976</v>
       </c>
       <c r="R29" t="n">
-        <v>6976237</v>
+        <v>6976536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3832,6 +3827,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336181</v>
+        <v>120336052</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,13 +3898,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450874</v>
+        <v>450710</v>
       </c>
       <c r="R30" t="n">
-        <v>6976230</v>
+        <v>6976591</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,6 +3934,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336052</v>
+        <v>120336640</v>
       </c>
       <c r="B31" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3976,21 +3981,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450710</v>
+        <v>450821</v>
       </c>
       <c r="R31" t="n">
-        <v>6976591</v>
+        <v>6976791</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,11 +4041,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336065</v>
+        <v>120336053</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450976</v>
+        <v>450750</v>
       </c>
       <c r="R32" t="n">
-        <v>6976536</v>
+        <v>6976700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336058</v>
+        <v>120336054</v>
       </c>
       <c r="B33" t="n">
-        <v>90594</v>
+        <v>78624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450840</v>
+        <v>450821</v>
       </c>
       <c r="R33" t="n">
-        <v>6976766</v>
+        <v>6976791</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336063</v>
+        <v>120336056</v>
       </c>
       <c r="B34" t="n">
-        <v>90594</v>
+        <v>79652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,25 +4293,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450895</v>
+        <v>450831</v>
       </c>
       <c r="R34" t="n">
-        <v>6976431</v>
+        <v>6976781</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4388,10 +4388,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336054</v>
+        <v>120336060</v>
       </c>
       <c r="B35" t="n">
-        <v>78624</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450821</v>
+        <v>450791</v>
       </c>
       <c r="R35" t="n">
-        <v>6976791</v>
+        <v>6976761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336051</v>
+        <v>120336172</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450701</v>
+        <v>450959</v>
       </c>
       <c r="R36" t="n">
-        <v>6976531</v>
+        <v>6976237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4571,11 +4571,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336061</v>
+        <v>120336059</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4618,21 +4613,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450820</v>
+        <v>450821</v>
       </c>
       <c r="R37" t="n">
-        <v>6976610</v>
+        <v>6976771</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4709,7 +4704,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336176</v>
+        <v>120336064</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -4749,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450917</v>
+        <v>450930</v>
       </c>
       <c r="R38" t="n">
-        <v>6976181</v>
+        <v>6976470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,6 +4780,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193947</v>
+        <v>120193961</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>77926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451001</v>
+        <v>451013</v>
       </c>
       <c r="R2" t="n">
-        <v>6976090</v>
+        <v>6976185</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -783,22 +778,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193935</v>
+        <v>120193923</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,26 +827,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451016</v>
+        <v>450990</v>
       </c>
       <c r="R3" t="n">
-        <v>6976094</v>
+        <v>6975968</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,11 +898,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -934,12 +924,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -957,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193901</v>
+        <v>120193935</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,26 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1006,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450966</v>
+        <v>451016</v>
       </c>
       <c r="R4" t="n">
-        <v>6975936</v>
+        <v>6976094</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,6 +1034,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1060,22 +1055,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193942</v>
+        <v>120193883</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,36 +1104,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1147,13 +1137,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451001</v>
+        <v>450948</v>
       </c>
       <c r="R5" t="n">
-        <v>6976090</v>
+        <v>6975913</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,11 +1175,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1216,12 +1201,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1239,10 +1224,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193883</v>
+        <v>120193947</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1255,31 +1240,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,13 +1278,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450948</v>
+        <v>451001</v>
       </c>
       <c r="R6" t="n">
-        <v>6975913</v>
+        <v>6976090</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1352,12 +1342,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193961</v>
+        <v>120193901</v>
       </c>
       <c r="B8" t="n">
-        <v>77926</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,26 +1517,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1560,10 +1550,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451013</v>
+        <v>450966</v>
       </c>
       <c r="R8" t="n">
-        <v>6976185</v>
+        <v>6975936</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1614,22 +1604,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1647,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193923</v>
+        <v>120193942</v>
       </c>
       <c r="B9" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,31 +1653,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1696,13 +1691,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R9" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,6 +1729,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1750,22 +1750,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222153</v>
+        <v>120222157</v>
       </c>
       <c r="B10" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450925</v>
+        <v>450970</v>
       </c>
       <c r="R10" t="n">
-        <v>6976466</v>
+        <v>6976524</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222155</v>
+        <v>120222148</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450928</v>
+        <v>450803</v>
       </c>
       <c r="R11" t="n">
-        <v>6976454</v>
+        <v>6976732</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222152</v>
+        <v>120222146</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>90923</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450724</v>
+        <v>450758</v>
       </c>
       <c r="R12" t="n">
-        <v>6976511</v>
+        <v>6976724</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222148</v>
+        <v>120222156</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450803</v>
+        <v>450980</v>
       </c>
       <c r="R13" t="n">
-        <v>6976732</v>
+        <v>6976531</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222147</v>
+        <v>120222155</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450759</v>
+        <v>450928</v>
       </c>
       <c r="R14" t="n">
-        <v>6976733</v>
+        <v>6976454</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222156</v>
+        <v>120222147</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450980</v>
+        <v>450759</v>
       </c>
       <c r="R15" t="n">
-        <v>6976531</v>
+        <v>6976733</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222146</v>
+        <v>120222152</v>
       </c>
       <c r="B16" t="n">
-        <v>90923</v>
+        <v>90594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,25 +2407,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450758</v>
+        <v>450724</v>
       </c>
       <c r="R16" t="n">
-        <v>6976724</v>
+        <v>6976511</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222157</v>
+        <v>120222151</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450970</v>
+        <v>450762</v>
       </c>
       <c r="R17" t="n">
-        <v>6976524</v>
+        <v>6976737</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222151</v>
+        <v>120222153</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450762</v>
+        <v>450925</v>
       </c>
       <c r="R18" t="n">
-        <v>6976737</v>
+        <v>6976466</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336176</v>
+        <v>120336058</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450917</v>
+        <v>450840</v>
       </c>
       <c r="R19" t="n">
-        <v>6976181</v>
+        <v>6976766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,6 +2777,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336169</v>
+        <v>120336062</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2819,21 +2824,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2848,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450959</v>
+        <v>450866</v>
       </c>
       <c r="R20" t="n">
-        <v>6976237</v>
+        <v>6976496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,6 +2884,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336063</v>
+        <v>120336055</v>
       </c>
       <c r="B21" t="n">
-        <v>90594</v>
+        <v>79659</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2917,25 +2927,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450895</v>
+        <v>450841</v>
       </c>
       <c r="R21" t="n">
-        <v>6976431</v>
+        <v>6976771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3114,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336181</v>
+        <v>120336640</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,21 +3140,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3154,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450874</v>
+        <v>450821</v>
       </c>
       <c r="R23" t="n">
-        <v>6976230</v>
+        <v>6976791</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3216,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336061</v>
+        <v>120336176</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,21 +3242,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450820</v>
+        <v>450917</v>
       </c>
       <c r="R24" t="n">
-        <v>6976610</v>
+        <v>6976181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,11 +3302,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,10 +3328,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336062</v>
+        <v>120336181</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,21 +3344,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,13 +3368,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450866</v>
+        <v>450874</v>
       </c>
       <c r="R25" t="n">
-        <v>6976496</v>
+        <v>6976230</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3399,11 +3404,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336051</v>
+        <v>120336064</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450701</v>
+        <v>450930</v>
       </c>
       <c r="R26" t="n">
-        <v>6976531</v>
+        <v>6976470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336058</v>
+        <v>120336169</v>
       </c>
       <c r="B27" t="n">
-        <v>90594</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,21 +3553,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450840</v>
+        <v>450959</v>
       </c>
       <c r="R27" t="n">
-        <v>6976766</v>
+        <v>6976237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,11 +3613,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,10 +3639,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336055</v>
+        <v>120336052</v>
       </c>
       <c r="B28" t="n">
-        <v>79659</v>
+        <v>82321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,25 +3651,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3684,10 +3679,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450841</v>
+        <v>450710</v>
       </c>
       <c r="R28" t="n">
-        <v>6976771</v>
+        <v>6976591</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3746,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336065</v>
+        <v>120336059</v>
       </c>
       <c r="B29" t="n">
         <v>78542</v>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450976</v>
+        <v>450821</v>
       </c>
       <c r="R29" t="n">
-        <v>6976536</v>
+        <v>6976771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,10 +3853,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336052</v>
+        <v>120336065</v>
       </c>
       <c r="B30" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,21 +3869,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450710</v>
+        <v>450976</v>
       </c>
       <c r="R30" t="n">
-        <v>6976591</v>
+        <v>6976536</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,10 +3960,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336640</v>
+        <v>120336056</v>
       </c>
       <c r="B31" t="n">
-        <v>86895</v>
+        <v>79652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3977,25 +3972,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4005,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450821</v>
+        <v>450831</v>
       </c>
       <c r="R31" t="n">
-        <v>6976791</v>
+        <v>6976781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4041,6 +4036,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336054</v>
+        <v>120336060</v>
       </c>
       <c r="B33" t="n">
-        <v>78624</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450821</v>
+        <v>450791</v>
       </c>
       <c r="R33" t="n">
-        <v>6976791</v>
+        <v>6976761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336056</v>
+        <v>120336054</v>
       </c>
       <c r="B34" t="n">
-        <v>79652</v>
+        <v>78624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,25 +4293,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450831</v>
+        <v>450821</v>
       </c>
       <c r="R34" t="n">
-        <v>6976781</v>
+        <v>6976791</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336060</v>
+        <v>120336061</v>
       </c>
       <c r="B35" t="n">
         <v>90598</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450791</v>
+        <v>450820</v>
       </c>
       <c r="R35" t="n">
-        <v>6976761</v>
+        <v>6976610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336059</v>
+        <v>120336063</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450821</v>
+        <v>450895</v>
       </c>
       <c r="R37" t="n">
-        <v>6976771</v>
+        <v>6976431</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336064</v>
+        <v>120336051</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4720,21 +4720,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450930</v>
+        <v>450701</v>
       </c>
       <c r="R38" t="n">
-        <v>6976470</v>
+        <v>6976531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336058</v>
+        <v>120336062</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450840</v>
+        <v>450866</v>
       </c>
       <c r="R19" t="n">
-        <v>6976766</v>
+        <v>6976496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336062</v>
+        <v>120336058</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450866</v>
+        <v>450840</v>
       </c>
       <c r="R20" t="n">
-        <v>6976496</v>
+        <v>6976766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336184</v>
+        <v>120336640</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3062,13 +3062,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450866</v>
+        <v>450821</v>
       </c>
       <c r="R22" t="n">
-        <v>6976252</v>
+        <v>6976791</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336640</v>
+        <v>120336184</v>
       </c>
       <c r="B23" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450821</v>
+        <v>450866</v>
       </c>
       <c r="R23" t="n">
-        <v>6976791</v>
+        <v>6976252</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336181</v>
+        <v>120336064</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450874</v>
+        <v>450930</v>
       </c>
       <c r="R25" t="n">
-        <v>6976230</v>
+        <v>6976470</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3404,6 +3404,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336064</v>
+        <v>120336181</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3470,13 +3475,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450930</v>
+        <v>450874</v>
       </c>
       <c r="R26" t="n">
-        <v>6976470</v>
+        <v>6976230</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3506,11 +3511,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193923</v>
+        <v>120193942</v>
       </c>
       <c r="B3" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,31 +827,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -860,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R3" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,6 +903,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,22 +924,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,7 +957,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193935</v>
+        <v>120193913</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -982,7 +992,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451016</v>
+        <v>450990</v>
       </c>
       <c r="R4" t="n">
-        <v>6976094</v>
+        <v>6975968</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,11 +1044,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1055,12 +1060,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1070,7 +1075,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193883</v>
+        <v>120193947</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,31 +1109,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1137,13 +1147,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450948</v>
+        <v>451001</v>
       </c>
       <c r="R5" t="n">
-        <v>6975913</v>
+        <v>6976090</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1201,12 +1211,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1224,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193947</v>
+        <v>120193935</v>
       </c>
       <c r="B6" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1240,36 +1250,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1278,10 +1283,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451001</v>
+        <v>451016</v>
       </c>
       <c r="R6" t="n">
-        <v>6976090</v>
+        <v>6976094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1316,6 +1321,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1332,22 +1342,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193913</v>
+        <v>120193923</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,26 +1391,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1468,22 +1478,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1501,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193901</v>
+        <v>120193883</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,26 +1527,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1550,10 +1560,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450966</v>
+        <v>450948</v>
       </c>
       <c r="R8" t="n">
-        <v>6975936</v>
+        <v>6975913</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1614,12 +1624,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1637,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193942</v>
+        <v>120193901</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1653,36 +1663,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1691,13 +1696,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451001</v>
+        <v>450966</v>
       </c>
       <c r="R9" t="n">
-        <v>6976090</v>
+        <v>6975936</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1729,11 +1734,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222157</v>
+        <v>120222153</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450970</v>
+        <v>450925</v>
       </c>
       <c r="R10" t="n">
-        <v>6976524</v>
+        <v>6976466</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222148</v>
+        <v>120222147</v>
       </c>
       <c r="B11" t="n">
         <v>90580</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450803</v>
+        <v>450759</v>
       </c>
       <c r="R11" t="n">
-        <v>6976732</v>
+        <v>6976733</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222146</v>
+        <v>120222148</v>
       </c>
       <c r="B12" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450758</v>
+        <v>450803</v>
       </c>
       <c r="R12" t="n">
-        <v>6976724</v>
+        <v>6976732</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222156</v>
+        <v>120222152</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450980</v>
+        <v>450724</v>
       </c>
       <c r="R13" t="n">
-        <v>6976531</v>
+        <v>6976511</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222155</v>
+        <v>120222156</v>
       </c>
       <c r="B14" t="n">
         <v>90598</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450928</v>
+        <v>450980</v>
       </c>
       <c r="R14" t="n">
-        <v>6976454</v>
+        <v>6976531</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222147</v>
+        <v>120222155</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450759</v>
+        <v>450928</v>
       </c>
       <c r="R15" t="n">
-        <v>6976733</v>
+        <v>6976454</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222152</v>
+        <v>120222151</v>
       </c>
       <c r="B16" t="n">
-        <v>90594</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450724</v>
+        <v>450762</v>
       </c>
       <c r="R16" t="n">
-        <v>6976511</v>
+        <v>6976737</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222151</v>
+        <v>120222146</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>90923</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450762</v>
+        <v>450758</v>
       </c>
       <c r="R17" t="n">
-        <v>6976737</v>
+        <v>6976724</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222153</v>
+        <v>120222157</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450925</v>
+        <v>450970</v>
       </c>
       <c r="R18" t="n">
-        <v>6976466</v>
+        <v>6976524</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336062</v>
+        <v>120336064</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450866</v>
+        <v>450930</v>
       </c>
       <c r="R19" t="n">
-        <v>6976496</v>
+        <v>6976470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336058</v>
+        <v>120336053</v>
       </c>
       <c r="B20" t="n">
-        <v>90594</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450840</v>
+        <v>450750</v>
       </c>
       <c r="R20" t="n">
-        <v>6976766</v>
+        <v>6976700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336055</v>
+        <v>120336054</v>
       </c>
       <c r="B21" t="n">
-        <v>79659</v>
+        <v>78624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450841</v>
+        <v>450821</v>
       </c>
       <c r="R21" t="n">
-        <v>6976771</v>
+        <v>6976791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336640</v>
+        <v>120336181</v>
       </c>
       <c r="B22" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3062,13 +3062,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450821</v>
+        <v>450874</v>
       </c>
       <c r="R22" t="n">
-        <v>6976791</v>
+        <v>6976230</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336184</v>
+        <v>120336055</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,25 +3136,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450866</v>
+        <v>450841</v>
       </c>
       <c r="R23" t="n">
-        <v>6976252</v>
+        <v>6976771</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3200,6 +3200,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336176</v>
+        <v>120336172</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450917</v>
+        <v>450959</v>
       </c>
       <c r="R24" t="n">
-        <v>6976181</v>
+        <v>6976237</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3328,7 +3333,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336064</v>
+        <v>120336065</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3368,10 +3373,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450930</v>
+        <v>450976</v>
       </c>
       <c r="R25" t="n">
-        <v>6976470</v>
+        <v>6976536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336181</v>
+        <v>120336169</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3456,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3475,13 +3480,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450874</v>
+        <v>450959</v>
       </c>
       <c r="R26" t="n">
-        <v>6976230</v>
+        <v>6976237</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3537,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336169</v>
+        <v>120336062</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,21 +3558,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3582,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450959</v>
+        <v>450866</v>
       </c>
       <c r="R27" t="n">
-        <v>6976237</v>
+        <v>6976496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,6 +3618,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3649,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336052</v>
+        <v>120336056</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3651,25 +3661,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3679,10 +3689,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450710</v>
+        <v>450831</v>
       </c>
       <c r="R28" t="n">
-        <v>6976591</v>
+        <v>6976781</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,10 +3756,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336059</v>
+        <v>120336063</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,21 +3772,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450821</v>
+        <v>450895</v>
       </c>
       <c r="R29" t="n">
-        <v>6976771</v>
+        <v>6976431</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336065</v>
+        <v>120336061</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,21 +3879,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3893,10 +3903,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450976</v>
+        <v>450820</v>
       </c>
       <c r="R30" t="n">
-        <v>6976536</v>
+        <v>6976610</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336056</v>
+        <v>120336051</v>
       </c>
       <c r="B31" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3972,25 +3982,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +4010,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450831</v>
+        <v>450701</v>
       </c>
       <c r="R31" t="n">
-        <v>6976781</v>
+        <v>6976531</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4067,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336053</v>
+        <v>120336184</v>
       </c>
       <c r="B32" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,20 +4089,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4107,13 +4117,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450750</v>
+        <v>450866</v>
       </c>
       <c r="R32" t="n">
-        <v>6976700</v>
+        <v>6976252</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,11 +4153,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336060</v>
+        <v>120336052</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450791</v>
+        <v>450710</v>
       </c>
       <c r="R33" t="n">
-        <v>6976761</v>
+        <v>6976591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,10 +4286,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336054</v>
+        <v>120336640</v>
       </c>
       <c r="B34" t="n">
-        <v>78624</v>
+        <v>86895</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4302,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4357,11 +4362,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336061</v>
+        <v>120336058</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450820</v>
+        <v>450840</v>
       </c>
       <c r="R35" t="n">
-        <v>6976610</v>
+        <v>6976766</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336172</v>
+        <v>120336176</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450959</v>
+        <v>450917</v>
       </c>
       <c r="R36" t="n">
-        <v>6976237</v>
+        <v>6976181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336063</v>
+        <v>120336059</v>
       </c>
       <c r="B37" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450895</v>
+        <v>450821</v>
       </c>
       <c r="R37" t="n">
-        <v>6976431</v>
+        <v>6976771</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336051</v>
+        <v>120336060</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4720,21 +4720,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450701</v>
+        <v>450791</v>
       </c>
       <c r="R38" t="n">
-        <v>6976531</v>
+        <v>6976761</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336172</v>
+        <v>120336065</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450959</v>
+        <v>450976</v>
       </c>
       <c r="R24" t="n">
-        <v>6976237</v>
+        <v>6976536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3307,6 +3307,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336065</v>
+        <v>120336172</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3373,10 +3378,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450976</v>
+        <v>450959</v>
       </c>
       <c r="R25" t="n">
-        <v>6976536</v>
+        <v>6976237</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,11 +3414,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336052</v>
+        <v>120336640</v>
       </c>
       <c r="B33" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450710</v>
+        <v>450821</v>
       </c>
       <c r="R33" t="n">
-        <v>6976591</v>
+        <v>6976791</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4255,11 +4255,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4286,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336640</v>
+        <v>120336052</v>
       </c>
       <c r="B34" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4326,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450821</v>
+        <v>450710</v>
       </c>
       <c r="R34" t="n">
-        <v>6976791</v>
+        <v>6976591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4362,6 +4357,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193961</v>
+        <v>120193913</v>
       </c>
       <c r="B2" t="n">
-        <v>77926</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451013</v>
+        <v>450990</v>
       </c>
       <c r="R2" t="n">
-        <v>6976185</v>
+        <v>6975968</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,22 +778,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193942</v>
+        <v>120193901</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,36 +827,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451001</v>
+        <v>450966</v>
       </c>
       <c r="R3" t="n">
-        <v>6976090</v>
+        <v>6975936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,11 +898,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -934,12 +924,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -957,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193913</v>
+        <v>120193923</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,26 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1060,22 +1050,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193947</v>
+        <v>120193883</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,36 +1099,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1147,13 +1132,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451001</v>
+        <v>450948</v>
       </c>
       <c r="R5" t="n">
-        <v>6976090</v>
+        <v>6975913</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1211,12 +1196,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1375,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193923</v>
+        <v>120193947</v>
       </c>
       <c r="B7" t="n">
-        <v>77926</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,31 +1376,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1424,13 +1414,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R7" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1478,22 +1468,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193883</v>
+        <v>120193961</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,26 +1517,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1560,10 +1550,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450948</v>
+        <v>451013</v>
       </c>
       <c r="R8" t="n">
-        <v>6975913</v>
+        <v>6976185</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1614,22 +1604,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1647,10 +1637,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193901</v>
+        <v>120193942</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,31 +1653,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1696,13 +1691,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450966</v>
+        <v>451001</v>
       </c>
       <c r="R9" t="n">
-        <v>6975936</v>
+        <v>6976090</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,6 +1729,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222153</v>
+        <v>120222157</v>
       </c>
       <c r="B10" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450925</v>
+        <v>450970</v>
       </c>
       <c r="R10" t="n">
-        <v>6976466</v>
+        <v>6976524</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222147</v>
+        <v>120222146</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,25 +1897,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450759</v>
+        <v>450758</v>
       </c>
       <c r="R11" t="n">
-        <v>6976733</v>
+        <v>6976724</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222148</v>
+        <v>120222152</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450803</v>
+        <v>450724</v>
       </c>
       <c r="R12" t="n">
-        <v>6976732</v>
+        <v>6976511</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222152</v>
+        <v>120222156</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450724</v>
+        <v>450980</v>
       </c>
       <c r="R13" t="n">
-        <v>6976511</v>
+        <v>6976531</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222156</v>
+        <v>120222153</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450980</v>
+        <v>450925</v>
       </c>
       <c r="R14" t="n">
-        <v>6976531</v>
+        <v>6976466</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222151</v>
+        <v>120222148</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450762</v>
+        <v>450803</v>
       </c>
       <c r="R16" t="n">
-        <v>6976737</v>
+        <v>6976732</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222146</v>
+        <v>120222151</v>
       </c>
       <c r="B17" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450758</v>
+        <v>450762</v>
       </c>
       <c r="R17" t="n">
-        <v>6976724</v>
+        <v>6976737</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222157</v>
+        <v>120222147</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450970</v>
+        <v>450759</v>
       </c>
       <c r="R18" t="n">
-        <v>6976524</v>
+        <v>6976733</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336064</v>
+        <v>120336061</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450930</v>
+        <v>450820</v>
       </c>
       <c r="R19" t="n">
-        <v>6976470</v>
+        <v>6976610</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336053</v>
+        <v>120336056</v>
       </c>
       <c r="B20" t="n">
-        <v>57431</v>
+        <v>79652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450750</v>
+        <v>450831</v>
       </c>
       <c r="R20" t="n">
-        <v>6976700</v>
+        <v>6976781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336054</v>
+        <v>120336060</v>
       </c>
       <c r="B21" t="n">
-        <v>78624</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450821</v>
+        <v>450791</v>
       </c>
       <c r="R21" t="n">
-        <v>6976791</v>
+        <v>6976761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336181</v>
+        <v>120336640</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3062,13 +3062,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450874</v>
+        <v>450821</v>
       </c>
       <c r="R22" t="n">
-        <v>6976230</v>
+        <v>6976791</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336055</v>
+        <v>120336062</v>
       </c>
       <c r="B23" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,25 +3136,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450841</v>
+        <v>450866</v>
       </c>
       <c r="R23" t="n">
-        <v>6976771</v>
+        <v>6976496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336065</v>
+        <v>120336054</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450976</v>
+        <v>450821</v>
       </c>
       <c r="R24" t="n">
-        <v>6976536</v>
+        <v>6976791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336172</v>
+        <v>120336059</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450959</v>
+        <v>450821</v>
       </c>
       <c r="R25" t="n">
-        <v>6976237</v>
+        <v>6976771</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,6 +3414,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3445,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336169</v>
+        <v>120336065</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3461,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450959</v>
+        <v>450976</v>
       </c>
       <c r="R26" t="n">
-        <v>6976237</v>
+        <v>6976536</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,6 +3521,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3552,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336062</v>
+        <v>120336053</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3554,25 +3564,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3582,10 +3592,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450866</v>
+        <v>450750</v>
       </c>
       <c r="R27" t="n">
-        <v>6976496</v>
+        <v>6976700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336056</v>
+        <v>120336063</v>
       </c>
       <c r="B28" t="n">
-        <v>79652</v>
+        <v>90594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3661,25 +3671,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3689,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450831</v>
+        <v>450895</v>
       </c>
       <c r="R28" t="n">
-        <v>6976781</v>
+        <v>6976431</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336063</v>
+        <v>120336184</v>
       </c>
       <c r="B29" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,21 +3782,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3796,13 +3806,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450895</v>
+        <v>450866</v>
       </c>
       <c r="R29" t="n">
-        <v>6976431</v>
+        <v>6976252</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3832,11 +3842,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3863,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336061</v>
+        <v>120336055</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>79659</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,25 +3880,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3903,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450820</v>
+        <v>450841</v>
       </c>
       <c r="R30" t="n">
-        <v>6976610</v>
+        <v>6976771</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4077,10 +4082,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336184</v>
+        <v>120336052</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4093,21 +4098,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4117,13 +4122,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450866</v>
+        <v>450710</v>
       </c>
       <c r="R32" t="n">
-        <v>6976252</v>
+        <v>6976591</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4153,6 +4158,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4189,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336640</v>
+        <v>120336064</v>
       </c>
       <c r="B33" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,21 +4205,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4229,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450821</v>
+        <v>450930</v>
       </c>
       <c r="R33" t="n">
-        <v>6976791</v>
+        <v>6976470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4255,6 +4265,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4296,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336052</v>
+        <v>120336181</v>
       </c>
       <c r="B34" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4312,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,13 +4336,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450710</v>
+        <v>450874</v>
       </c>
       <c r="R34" t="n">
-        <v>6976591</v>
+        <v>6976230</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,11 +4372,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336058</v>
+        <v>120336172</v>
       </c>
       <c r="B35" t="n">
-        <v>90594</v>
+        <v>90864</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,21 +4414,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4428,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450840</v>
+        <v>450959</v>
       </c>
       <c r="R35" t="n">
-        <v>6976766</v>
+        <v>6976237</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4464,11 +4474,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,10 +4500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336176</v>
+        <v>120336058</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4516,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,10 +4540,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450917</v>
+        <v>450840</v>
       </c>
       <c r="R36" t="n">
-        <v>6976181</v>
+        <v>6976766</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4571,6 +4576,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4597,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336059</v>
+        <v>120336169</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4613,21 +4623,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450821</v>
+        <v>450959</v>
       </c>
       <c r="R37" t="n">
-        <v>6976771</v>
+        <v>6976237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4673,11 +4683,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4704,10 +4709,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336060</v>
+        <v>120336176</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4720,21 +4725,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,10 +4749,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450791</v>
+        <v>450917</v>
       </c>
       <c r="R38" t="n">
-        <v>6976761</v>
+        <v>6976181</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4780,11 +4785,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193913</v>
+        <v>120193883</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450990</v>
+        <v>450948</v>
       </c>
       <c r="R2" t="n">
-        <v>6975968</v>
+        <v>6975913</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -947,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193923</v>
+        <v>120193935</v>
       </c>
       <c r="B4" t="n">
-        <v>77926</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450990</v>
+        <v>451016</v>
       </c>
       <c r="R4" t="n">
-        <v>6975968</v>
+        <v>6976094</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,6 +1034,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1060,12 +1065,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193883</v>
+        <v>120193961</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,26 +1104,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,10 +1137,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450948</v>
+        <v>451013</v>
       </c>
       <c r="R5" t="n">
-        <v>6975913</v>
+        <v>6976185</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1186,22 +1191,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1219,10 +1224,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193935</v>
+        <v>120193942</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,21 +1240,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1259,7 +1264,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1268,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451016</v>
+        <v>451001</v>
       </c>
       <c r="R6" t="n">
-        <v>6976094</v>
+        <v>6976090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,7 +1318,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Garnlav på tall</t>
+          <t>På samma låga som rosenticka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,22 +1337,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193947</v>
+        <v>120193923</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>77926</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,36 +1386,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1414,13 +1419,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451001</v>
+        <v>450990</v>
       </c>
       <c r="R7" t="n">
-        <v>6976090</v>
+        <v>6975968</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1468,22 +1473,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193961</v>
+        <v>120193947</v>
       </c>
       <c r="B8" t="n">
-        <v>77926</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,31 +1522,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1550,13 +1560,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451013</v>
+        <v>451001</v>
       </c>
       <c r="R8" t="n">
-        <v>6976185</v>
+        <v>6976090</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1604,22 +1614,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1637,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193942</v>
+        <v>120193913</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1653,36 +1663,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1691,13 +1696,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451001</v>
+        <v>450990</v>
       </c>
       <c r="R9" t="n">
-        <v>6976090</v>
+        <v>6975968</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1729,11 +1734,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222157</v>
+        <v>120222148</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450970</v>
+        <v>450803</v>
       </c>
       <c r="R10" t="n">
-        <v>6976524</v>
+        <v>6976732</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222146</v>
+        <v>120222153</v>
       </c>
       <c r="B11" t="n">
-        <v>90923</v>
+        <v>90594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,25 +1897,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450758</v>
+        <v>450925</v>
       </c>
       <c r="R11" t="n">
-        <v>6976724</v>
+        <v>6976466</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222152</v>
+        <v>120222155</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450724</v>
+        <v>450928</v>
       </c>
       <c r="R12" t="n">
-        <v>6976511</v>
+        <v>6976454</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222156</v>
+        <v>120222151</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450980</v>
+        <v>450762</v>
       </c>
       <c r="R13" t="n">
-        <v>6976531</v>
+        <v>6976737</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222153</v>
+        <v>120222146</v>
       </c>
       <c r="B14" t="n">
-        <v>90594</v>
+        <v>90923</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450925</v>
+        <v>450758</v>
       </c>
       <c r="R14" t="n">
-        <v>6976466</v>
+        <v>6976724</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222155</v>
+        <v>120222152</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450928</v>
+        <v>450724</v>
       </c>
       <c r="R15" t="n">
-        <v>6976454</v>
+        <v>6976511</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222148</v>
+        <v>120222156</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450803</v>
+        <v>450980</v>
       </c>
       <c r="R16" t="n">
-        <v>6976732</v>
+        <v>6976531</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222151</v>
+        <v>120222157</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450762</v>
+        <v>450970</v>
       </c>
       <c r="R17" t="n">
-        <v>6976737</v>
+        <v>6976524</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336061</v>
+        <v>120336181</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450820</v>
+        <v>450874</v>
       </c>
       <c r="R19" t="n">
-        <v>6976610</v>
+        <v>6976230</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,11 +2777,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336056</v>
+        <v>120336055</v>
       </c>
       <c r="B20" t="n">
-        <v>79652</v>
+        <v>79659</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,21 +2819,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450831</v>
+        <v>450841</v>
       </c>
       <c r="R20" t="n">
-        <v>6976781</v>
+        <v>6976771</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,10 +2910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336060</v>
+        <v>120336052</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2926,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450791</v>
+        <v>450710</v>
       </c>
       <c r="R21" t="n">
-        <v>6976761</v>
+        <v>6976591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336640</v>
+        <v>120336053</v>
       </c>
       <c r="B22" t="n">
-        <v>86895</v>
+        <v>57431</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3034,25 +3029,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450821</v>
+        <v>450750</v>
       </c>
       <c r="R22" t="n">
-        <v>6976791</v>
+        <v>6976700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3098,6 +3093,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336062</v>
+        <v>120336063</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450866</v>
+        <v>450895</v>
       </c>
       <c r="R23" t="n">
-        <v>6976496</v>
+        <v>6976431</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336054</v>
+        <v>120336062</v>
       </c>
       <c r="B24" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450821</v>
+        <v>450866</v>
       </c>
       <c r="R24" t="n">
-        <v>6976791</v>
+        <v>6976496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336059</v>
+        <v>120336640</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
         <v>450821</v>
       </c>
       <c r="R25" t="n">
-        <v>6976771</v>
+        <v>6976791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,11 +3414,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,7 +3440,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336065</v>
+        <v>120336176</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450976</v>
+        <v>450917</v>
       </c>
       <c r="R26" t="n">
-        <v>6976536</v>
+        <v>6976181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,11 +3516,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336053</v>
+        <v>120336184</v>
       </c>
       <c r="B27" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,20 +3554,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3592,13 +3582,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450750</v>
+        <v>450866</v>
       </c>
       <c r="R27" t="n">
-        <v>6976700</v>
+        <v>6976252</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,11 +3618,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336063</v>
+        <v>120336169</v>
       </c>
       <c r="B28" t="n">
-        <v>90594</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,21 +3660,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3684,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450895</v>
+        <v>450959</v>
       </c>
       <c r="R28" t="n">
-        <v>6976431</v>
+        <v>6976237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,11 +3720,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336184</v>
+        <v>120336060</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,21 +3762,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3806,13 +3786,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450866</v>
+        <v>450791</v>
       </c>
       <c r="R29" t="n">
-        <v>6976252</v>
+        <v>6976761</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3842,6 +3822,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3868,10 +3853,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336055</v>
+        <v>120336064</v>
       </c>
       <c r="B30" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,25 +3865,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3908,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450841</v>
+        <v>450930</v>
       </c>
       <c r="R30" t="n">
-        <v>6976771</v>
+        <v>6976470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,10 +3960,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336051</v>
+        <v>120336065</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3991,21 +3976,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4015,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450701</v>
+        <v>450976</v>
       </c>
       <c r="R31" t="n">
-        <v>6976531</v>
+        <v>6976536</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4082,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336052</v>
+        <v>120336172</v>
       </c>
       <c r="B32" t="n">
-        <v>82321</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4098,21 +4083,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450710</v>
+        <v>450959</v>
       </c>
       <c r="R32" t="n">
-        <v>6976591</v>
+        <v>6976237</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4158,11 +4143,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,10 +4169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336064</v>
+        <v>120336056</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,25 +4181,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4229,10 +4209,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450930</v>
+        <v>450831</v>
       </c>
       <c r="R33" t="n">
-        <v>6976470</v>
+        <v>6976781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4296,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336181</v>
+        <v>120336058</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,21 +4292,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4336,13 +4316,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450874</v>
+        <v>450840</v>
       </c>
       <c r="R34" t="n">
-        <v>6976230</v>
+        <v>6976766</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4372,6 +4352,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4398,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336172</v>
+        <v>120336054</v>
       </c>
       <c r="B35" t="n">
-        <v>90864</v>
+        <v>78624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450959</v>
+        <v>450821</v>
       </c>
       <c r="R35" t="n">
-        <v>6976237</v>
+        <v>6976791</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,6 +4459,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4500,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336058</v>
+        <v>120336061</v>
       </c>
       <c r="B36" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,21 +4506,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4540,10 +4530,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450840</v>
+        <v>450820</v>
       </c>
       <c r="R36" t="n">
-        <v>6976766</v>
+        <v>6976610</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4607,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336169</v>
+        <v>120336059</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,21 +4613,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4647,10 +4637,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450959</v>
+        <v>450821</v>
       </c>
       <c r="R37" t="n">
-        <v>6976237</v>
+        <v>6976771</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4683,6 +4673,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,10 +4704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336176</v>
+        <v>120336051</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4725,21 +4720,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4749,10 +4744,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450917</v>
+        <v>450701</v>
       </c>
       <c r="R38" t="n">
-        <v>6976181</v>
+        <v>6976531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4785,6 +4780,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193961</v>
+        <v>120193942</v>
       </c>
       <c r="B5" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,31 +1104,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1137,13 +1142,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451013</v>
+        <v>451001</v>
       </c>
       <c r="R5" t="n">
-        <v>6976185</v>
+        <v>6976090</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,6 +1180,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1191,22 +1201,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1224,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193942</v>
+        <v>120193961</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>77926</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1240,36 +1250,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1278,13 +1283,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451001</v>
+        <v>451013</v>
       </c>
       <c r="R6" t="n">
-        <v>6976090</v>
+        <v>6976185</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,11 +1321,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222156</v>
+        <v>120222147</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450980</v>
+        <v>450759</v>
       </c>
       <c r="R16" t="n">
-        <v>6976531</v>
+        <v>6976733</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222157</v>
+        <v>120222156</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450970</v>
+        <v>450980</v>
       </c>
       <c r="R17" t="n">
-        <v>6976524</v>
+        <v>6976531</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222147</v>
+        <v>120222157</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450759</v>
+        <v>450970</v>
       </c>
       <c r="R18" t="n">
-        <v>6976733</v>
+        <v>6976524</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336062</v>
+        <v>120336640</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450866</v>
+        <v>450821</v>
       </c>
       <c r="R24" t="n">
-        <v>6976496</v>
+        <v>6976791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3307,11 +3307,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3338,10 +3333,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336640</v>
+        <v>120336062</v>
       </c>
       <c r="B25" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,21 +3349,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3378,10 +3373,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450821</v>
+        <v>450866</v>
       </c>
       <c r="R25" t="n">
-        <v>6976791</v>
+        <v>6976496</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,6 +3409,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336176</v>
+        <v>120336184</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,13 +3480,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450917</v>
+        <v>450866</v>
       </c>
       <c r="R26" t="n">
-        <v>6976181</v>
+        <v>6976252</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336184</v>
+        <v>120336176</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3582,13 +3582,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450866</v>
+        <v>450917</v>
       </c>
       <c r="R27" t="n">
-        <v>6976252</v>
+        <v>6976181</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336060</v>
+        <v>120336064</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450791</v>
+        <v>450930</v>
       </c>
       <c r="R29" t="n">
-        <v>6976761</v>
+        <v>6976470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336064</v>
+        <v>120336060</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450930</v>
+        <v>450791</v>
       </c>
       <c r="R30" t="n">
-        <v>6976470</v>
+        <v>6976761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193883</v>
+        <v>120193961</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>77926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450948</v>
+        <v>451013</v>
       </c>
       <c r="R2" t="n">
-        <v>6975913</v>
+        <v>6976185</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,22 +778,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193901</v>
+        <v>120193883</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,26 +827,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450966</v>
+        <v>450948</v>
       </c>
       <c r="R3" t="n">
-        <v>6975936</v>
+        <v>6975913</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -924,12 +924,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193942</v>
+        <v>120193947</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,26 +1104,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1178,11 +1178,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1234,10 +1229,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193961</v>
+        <v>120193913</v>
       </c>
       <c r="B6" t="n">
-        <v>77926</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,26 +1245,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1283,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451013</v>
+        <v>450990</v>
       </c>
       <c r="R6" t="n">
-        <v>6976185</v>
+        <v>6975968</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1337,22 +1332,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193923</v>
+        <v>120193942</v>
       </c>
       <c r="B7" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,31 +1381,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R7" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1457,6 +1457,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1473,22 +1478,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193947</v>
+        <v>120193923</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>77926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1522,36 +1527,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451001</v>
+        <v>450990</v>
       </c>
       <c r="R8" t="n">
-        <v>6976090</v>
+        <v>6975968</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1614,22 +1614,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193913</v>
+        <v>120193901</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,26 +1663,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450990</v>
+        <v>450966</v>
       </c>
       <c r="R9" t="n">
-        <v>6975968</v>
+        <v>6975936</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222148</v>
+        <v>120222147</v>
       </c>
       <c r="B10" t="n">
         <v>90580</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450803</v>
+        <v>450759</v>
       </c>
       <c r="R10" t="n">
-        <v>6976732</v>
+        <v>6976733</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222153</v>
+        <v>120222156</v>
       </c>
       <c r="B11" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450925</v>
+        <v>450980</v>
       </c>
       <c r="R11" t="n">
-        <v>6976466</v>
+        <v>6976531</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222155</v>
+        <v>120222151</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450928</v>
+        <v>450762</v>
       </c>
       <c r="R12" t="n">
-        <v>6976454</v>
+        <v>6976737</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222151</v>
+        <v>120222155</v>
       </c>
       <c r="B13" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450762</v>
+        <v>450928</v>
       </c>
       <c r="R13" t="n">
-        <v>6976737</v>
+        <v>6976454</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222146</v>
+        <v>120222153</v>
       </c>
       <c r="B14" t="n">
-        <v>90923</v>
+        <v>90594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450758</v>
+        <v>450925</v>
       </c>
       <c r="R14" t="n">
-        <v>6976724</v>
+        <v>6976466</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222152</v>
+        <v>120222146</v>
       </c>
       <c r="B15" t="n">
-        <v>90594</v>
+        <v>90923</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450724</v>
+        <v>450758</v>
       </c>
       <c r="R15" t="n">
-        <v>6976511</v>
+        <v>6976724</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222147</v>
+        <v>120222152</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450759</v>
+        <v>450724</v>
       </c>
       <c r="R16" t="n">
-        <v>6976733</v>
+        <v>6976511</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222156</v>
+        <v>120222157</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450980</v>
+        <v>450970</v>
       </c>
       <c r="R17" t="n">
-        <v>6976531</v>
+        <v>6976524</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222157</v>
+        <v>120222148</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450970</v>
+        <v>450803</v>
       </c>
       <c r="R18" t="n">
-        <v>6976524</v>
+        <v>6976732</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336181</v>
+        <v>120336058</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450874</v>
+        <v>450840</v>
       </c>
       <c r="R19" t="n">
-        <v>6976230</v>
+        <v>6976766</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,6 +2777,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336055</v>
+        <v>120336064</v>
       </c>
       <c r="B20" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,25 +2820,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2848,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450841</v>
+        <v>450930</v>
       </c>
       <c r="R20" t="n">
-        <v>6976771</v>
+        <v>6976470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2910,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336052</v>
+        <v>120336640</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2926,21 +2931,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450710</v>
+        <v>450821</v>
       </c>
       <c r="R21" t="n">
-        <v>6976591</v>
+        <v>6976791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,11 +2991,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336053</v>
+        <v>120336061</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,25 +3029,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450750</v>
+        <v>450820</v>
       </c>
       <c r="R22" t="n">
-        <v>6976700</v>
+        <v>6976610</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336063</v>
+        <v>120336055</v>
       </c>
       <c r="B23" t="n">
-        <v>90594</v>
+        <v>79659</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,25 +3136,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450895</v>
+        <v>450841</v>
       </c>
       <c r="R23" t="n">
-        <v>6976431</v>
+        <v>6976771</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336640</v>
+        <v>120336052</v>
       </c>
       <c r="B24" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450821</v>
+        <v>450710</v>
       </c>
       <c r="R24" t="n">
-        <v>6976791</v>
+        <v>6976591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3307,6 +3307,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336062</v>
+        <v>120336181</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3373,13 +3378,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450866</v>
+        <v>450874</v>
       </c>
       <c r="R25" t="n">
-        <v>6976496</v>
+        <v>6976230</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3409,11 +3414,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336184</v>
+        <v>120336065</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,13 +3480,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450866</v>
+        <v>450976</v>
       </c>
       <c r="R26" t="n">
-        <v>6976252</v>
+        <v>6976536</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3516,6 +3516,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3547,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336176</v>
+        <v>120336172</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,21 +3563,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450917</v>
+        <v>450959</v>
       </c>
       <c r="R27" t="n">
-        <v>6976181</v>
+        <v>6976237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3746,10 +3751,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336064</v>
+        <v>120336051</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,21 +3767,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450930</v>
+        <v>450701</v>
       </c>
       <c r="R29" t="n">
-        <v>6976470</v>
+        <v>6976531</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,10 +3858,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336060</v>
+        <v>120336054</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>78624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3893,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450791</v>
+        <v>450821</v>
       </c>
       <c r="R30" t="n">
-        <v>6976761</v>
+        <v>6976791</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,7 +3965,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336065</v>
+        <v>120336176</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450976</v>
+        <v>450917</v>
       </c>
       <c r="R31" t="n">
-        <v>6976536</v>
+        <v>6976181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,11 +4041,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336172</v>
+        <v>120336056</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>79652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450959</v>
+        <v>450831</v>
       </c>
       <c r="R32" t="n">
-        <v>6976237</v>
+        <v>6976781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4143,6 +4143,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336056</v>
+        <v>120336063</v>
       </c>
       <c r="B33" t="n">
-        <v>79652</v>
+        <v>90594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,25 +4186,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4209,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450831</v>
+        <v>450895</v>
       </c>
       <c r="R33" t="n">
-        <v>6976781</v>
+        <v>6976431</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336058</v>
+        <v>120336062</v>
       </c>
       <c r="B34" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4316,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450840</v>
+        <v>450866</v>
       </c>
       <c r="R34" t="n">
-        <v>6976766</v>
+        <v>6976496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4383,10 +4388,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336054</v>
+        <v>120336059</v>
       </c>
       <c r="B35" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4404,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,7 +4431,7 @@
         <v>450821</v>
       </c>
       <c r="R35" t="n">
-        <v>6976791</v>
+        <v>6976771</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4495,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336061</v>
+        <v>120336060</v>
       </c>
       <c r="B36" t="n">
         <v>90598</v>
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450820</v>
+        <v>450791</v>
       </c>
       <c r="R36" t="n">
-        <v>6976610</v>
+        <v>6976761</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4597,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336059</v>
+        <v>120336053</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4609,25 +4614,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4637,10 +4642,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450821</v>
+        <v>450750</v>
       </c>
       <c r="R37" t="n">
-        <v>6976771</v>
+        <v>6976700</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4709,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336051</v>
+        <v>120336184</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4720,21 +4725,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4744,13 +4749,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450701</v>
+        <v>450866</v>
       </c>
       <c r="R38" t="n">
-        <v>6976531</v>
+        <v>6976252</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4780,11 +4785,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193961</v>
+        <v>120193942</v>
       </c>
       <c r="B2" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451013</v>
+        <v>451001</v>
       </c>
       <c r="R2" t="n">
-        <v>6976185</v>
+        <v>6976090</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +767,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,22 +788,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,7 +821,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120193883</v>
+        <v>120193935</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -846,7 +856,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,13 +870,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450948</v>
+        <v>451016</v>
       </c>
       <c r="R3" t="n">
-        <v>6975913</v>
+        <v>6976094</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,6 +908,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,12 +929,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -929,7 +944,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,7 +962,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193935</v>
+        <v>120193913</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -982,7 +997,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,13 +1011,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451016</v>
+        <v>450990</v>
       </c>
       <c r="R4" t="n">
-        <v>6976094</v>
+        <v>6975968</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,11 +1049,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1055,12 +1065,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1070,7 +1080,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193947</v>
+        <v>120193961</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>77926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,36 +1114,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1142,13 +1147,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451001</v>
+        <v>451013</v>
       </c>
       <c r="R5" t="n">
-        <v>6976090</v>
+        <v>6976185</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1196,22 +1201,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1229,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193913</v>
+        <v>120193901</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,26 +1250,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1278,10 +1283,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450990</v>
+        <v>450966</v>
       </c>
       <c r="R6" t="n">
-        <v>6975968</v>
+        <v>6975936</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1342,12 +1347,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1365,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193942</v>
+        <v>120193883</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,36 +1386,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451001</v>
+        <v>450948</v>
       </c>
       <c r="R7" t="n">
-        <v>6976090</v>
+        <v>6975913</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1457,11 +1457,6 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1488,12 +1483,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193923</v>
+        <v>120193947</v>
       </c>
       <c r="B8" t="n">
-        <v>77926</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,31 +1522,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450990</v>
+        <v>451001</v>
       </c>
       <c r="R8" t="n">
-        <v>6975968</v>
+        <v>6976090</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1614,22 +1614,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193901</v>
+        <v>120193923</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>77926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,26 +1663,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450966</v>
+        <v>450990</v>
       </c>
       <c r="R9" t="n">
-        <v>6975936</v>
+        <v>6975968</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1750,22 +1750,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222147</v>
+        <v>120222157</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450759</v>
+        <v>450970</v>
       </c>
       <c r="R10" t="n">
-        <v>6976733</v>
+        <v>6976524</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222156</v>
+        <v>120222148</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450980</v>
+        <v>450803</v>
       </c>
       <c r="R11" t="n">
-        <v>6976531</v>
+        <v>6976732</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222151</v>
+        <v>120222152</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450762</v>
+        <v>450724</v>
       </c>
       <c r="R12" t="n">
-        <v>6976737</v>
+        <v>6976511</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222155</v>
+        <v>120222146</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>90923</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,25 +2101,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450928</v>
+        <v>450758</v>
       </c>
       <c r="R13" t="n">
-        <v>6976454</v>
+        <v>6976724</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222153</v>
+        <v>120222156</v>
       </c>
       <c r="B14" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450925</v>
+        <v>450980</v>
       </c>
       <c r="R14" t="n">
-        <v>6976466</v>
+        <v>6976531</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222146</v>
+        <v>120222151</v>
       </c>
       <c r="B15" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450758</v>
+        <v>450762</v>
       </c>
       <c r="R15" t="n">
-        <v>6976724</v>
+        <v>6976737</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222152</v>
+        <v>120222155</v>
       </c>
       <c r="B16" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450724</v>
+        <v>450928</v>
       </c>
       <c r="R16" t="n">
-        <v>6976511</v>
+        <v>6976454</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222157</v>
+        <v>120222147</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,21 +2513,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450970</v>
+        <v>450759</v>
       </c>
       <c r="R17" t="n">
-        <v>6976524</v>
+        <v>6976733</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222148</v>
+        <v>120222153</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450803</v>
+        <v>450925</v>
       </c>
       <c r="R18" t="n">
-        <v>6976732</v>
+        <v>6976466</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336058</v>
+        <v>120336181</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450840</v>
+        <v>450874</v>
       </c>
       <c r="R19" t="n">
-        <v>6976766</v>
+        <v>6976230</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,11 +2777,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336064</v>
+        <v>120336053</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,25 +2815,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450930</v>
+        <v>450750</v>
       </c>
       <c r="R20" t="n">
-        <v>6976470</v>
+        <v>6976700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,10 +2910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336640</v>
+        <v>120336060</v>
       </c>
       <c r="B21" t="n">
-        <v>86895</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2926,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450821</v>
+        <v>450791</v>
       </c>
       <c r="R21" t="n">
-        <v>6976791</v>
+        <v>6976761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,6 +2986,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336061</v>
+        <v>120336064</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,21 +3033,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450820</v>
+        <v>450930</v>
       </c>
       <c r="R22" t="n">
-        <v>6976610</v>
+        <v>6976470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336055</v>
+        <v>120336176</v>
       </c>
       <c r="B23" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3136,25 +3136,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450841</v>
+        <v>450917</v>
       </c>
       <c r="R23" t="n">
-        <v>6976771</v>
+        <v>6976181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,11 +3200,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336052</v>
+        <v>120336062</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3242,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450710</v>
+        <v>450866</v>
       </c>
       <c r="R24" t="n">
-        <v>6976591</v>
+        <v>6976496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,10 +3333,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336181</v>
+        <v>120336054</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,21 +3349,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3378,13 +3373,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450874</v>
+        <v>450821</v>
       </c>
       <c r="R25" t="n">
-        <v>6976230</v>
+        <v>6976791</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3414,6 +3409,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336065</v>
+        <v>120336172</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450976</v>
+        <v>450959</v>
       </c>
       <c r="R26" t="n">
-        <v>6976536</v>
+        <v>6976237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,11 +3516,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336172</v>
+        <v>120336640</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>86895</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,21 +3558,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450959</v>
+        <v>450821</v>
       </c>
       <c r="R27" t="n">
-        <v>6976237</v>
+        <v>6976791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336169</v>
+        <v>120336065</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450959</v>
+        <v>450976</v>
       </c>
       <c r="R28" t="n">
-        <v>6976237</v>
+        <v>6976536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,6 +3720,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336051</v>
+        <v>120336055</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>79659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450701</v>
+        <v>450841</v>
       </c>
       <c r="R29" t="n">
-        <v>6976531</v>
+        <v>6976771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,10 +3858,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336054</v>
+        <v>120336052</v>
       </c>
       <c r="B30" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450821</v>
+        <v>450710</v>
       </c>
       <c r="R30" t="n">
-        <v>6976791</v>
+        <v>6976591</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336176</v>
+        <v>120336063</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450917</v>
+        <v>450895</v>
       </c>
       <c r="R31" t="n">
-        <v>6976181</v>
+        <v>6976431</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4041,6 +4041,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4072,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336056</v>
+        <v>120336058</v>
       </c>
       <c r="B32" t="n">
-        <v>79652</v>
+        <v>90594</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,25 +4084,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450831</v>
+        <v>450840</v>
       </c>
       <c r="R32" t="n">
-        <v>6976781</v>
+        <v>6976766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336063</v>
+        <v>120336051</v>
       </c>
       <c r="B33" t="n">
-        <v>90594</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450895</v>
+        <v>450701</v>
       </c>
       <c r="R33" t="n">
-        <v>6976431</v>
+        <v>6976531</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,10 +4286,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336062</v>
+        <v>120336169</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4302,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450866</v>
+        <v>450959</v>
       </c>
       <c r="R34" t="n">
-        <v>6976496</v>
+        <v>6976237</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,11 +4362,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120336059</v>
+        <v>120336056</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4400,25 +4400,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450821</v>
+        <v>450831</v>
       </c>
       <c r="R35" t="n">
-        <v>6976771</v>
+        <v>6976781</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120336060</v>
+        <v>120336184</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450791</v>
+        <v>450866</v>
       </c>
       <c r="R36" t="n">
-        <v>6976761</v>
+        <v>6976252</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4571,11 +4571,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120336053</v>
+        <v>120336059</v>
       </c>
       <c r="B37" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4614,25 +4609,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450750</v>
+        <v>450821</v>
       </c>
       <c r="R37" t="n">
-        <v>6976700</v>
+        <v>6976771</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4709,10 +4704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120336184</v>
+        <v>120336061</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4725,21 +4720,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4749,13 +4744,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450866</v>
+        <v>450820</v>
       </c>
       <c r="R38" t="n">
-        <v>6976252</v>
+        <v>6976610</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4785,6 +4780,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120193961</v>
+        <v>120336640</v>
       </c>
       <c r="B2" t="n">
-        <v>77926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451013</v>
+        <v>450821</v>
       </c>
       <c r="R2" t="n">
-        <v>6976185</v>
+        <v>6976791</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,31 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -814,12 +775,7 @@
         <v>120193947</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -952,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120193923</v>
+        <v>120222151</v>
       </c>
       <c r="B4" t="n">
-        <v>77926</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,43 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
+          <t>Marntallsflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450990</v>
+        <v>450762</v>
       </c>
       <c r="R4" t="n">
-        <v>6975968</v>
+        <v>6976737</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1031,12 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,56 +989,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120193942</v>
+        <v>120336172</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,48 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451001</v>
+        <v>450959</v>
       </c>
       <c r="R5" t="n">
-        <v>6976090</v>
+        <v>6976237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,17 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På samma låga som rosenticka.</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,31 +1086,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1234,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120193901</v>
+        <v>120336054</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,46 +1113,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450966</v>
+        <v>450821</v>
       </c>
       <c r="R6" t="n">
-        <v>6975936</v>
+        <v>6976791</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,12 +1167,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,31 +1188,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1370,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120193883</v>
+        <v>120193942</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,31 +1215,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1419,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450948</v>
+        <v>451001</v>
       </c>
       <c r="R7" t="n">
-        <v>6975913</v>
+        <v>6976090</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1457,6 +1291,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På samma låga som rosenticka.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1483,12 +1322,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1506,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120193935</v>
+        <v>120222147</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,46 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
+          <t>Marntallsflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451016</v>
+        <v>450759</v>
       </c>
       <c r="R8" t="n">
-        <v>6976094</v>
+        <v>6976733</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1585,17 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,56 +1426,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120193913</v>
+        <v>120222148</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,43 +1453,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
+          <t>Marntallsflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450990</v>
+        <v>450803</v>
       </c>
       <c r="R9" t="n">
-        <v>6975968</v>
+        <v>6976732</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1726,12 +1507,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1742,56 +1523,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222147</v>
+        <v>120336169</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1819,17 +1570,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450759</v>
+        <v>450959</v>
       </c>
       <c r="R10" t="n">
-        <v>6976733</v>
+        <v>6976237</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1873,49 +1624,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222155</v>
+        <v>120222152</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450928</v>
+        <v>450724</v>
       </c>
       <c r="R11" t="n">
-        <v>6976454</v>
+        <v>6976511</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1987,37 +1733,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222156</v>
+        <v>120222153</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450980</v>
+        <v>450925</v>
       </c>
       <c r="R12" t="n">
-        <v>6976531</v>
+        <v>6976466</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2089,19 +1830,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222152</v>
+        <v>120336058</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2125,17 +1861,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450724</v>
+        <v>450840</v>
       </c>
       <c r="R13" t="n">
-        <v>6976511</v>
+        <v>6976766</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2165,6 +1901,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,65 +1920,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222151</v>
+        <v>120336063</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450762</v>
+        <v>450895</v>
       </c>
       <c r="R14" t="n">
-        <v>6976737</v>
+        <v>6976431</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2267,6 +2003,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,62 +2022,66 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222146</v>
+        <v>120193901</v>
       </c>
       <c r="B15" t="n">
-        <v>90923</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450758</v>
+        <v>450966</v>
       </c>
       <c r="R15" t="n">
-        <v>6976724</v>
+        <v>6975936</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2363,12 +2108,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,31 +2124,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222157</v>
+        <v>120336052</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,37 +2176,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450970</v>
+        <v>450710</v>
       </c>
       <c r="R16" t="n">
-        <v>6976524</v>
+        <v>6976591</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2471,6 +2236,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,49 +2255,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222148</v>
+        <v>120222146</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450803</v>
+        <v>450758</v>
       </c>
       <c r="R17" t="n">
-        <v>6976732</v>
+        <v>6976724</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2599,50 +2364,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222153</v>
+        <v>120193883</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Marntallsflon, Jmt</t>
+          <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450925</v>
+        <v>450948</v>
       </c>
       <c r="R18" t="n">
-        <v>6976466</v>
+        <v>6975913</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2669,12 +2438,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,35 +2454,55 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Johan Eliasson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120336176</v>
+        <v>120193913</v>
       </c>
       <c r="B19" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2734,20 +2523,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450917</v>
+        <v>450990</v>
       </c>
       <c r="R19" t="n">
-        <v>6976181</v>
+        <v>6975968</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2771,12 +2569,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,6 +2585,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2803,50 +2626,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120336055</v>
+        <v>120193935</v>
       </c>
       <c r="B20" t="n">
-        <v>79681</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450841</v>
+        <v>451016</v>
       </c>
       <c r="R20" t="n">
-        <v>6976771</v>
+        <v>6976094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,17 +2700,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,6 +2721,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2910,53 +2762,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120336169</v>
+        <v>120222157</v>
       </c>
       <c r="B21" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
+          <t>Marntallsflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450959</v>
+        <v>450970</v>
       </c>
       <c r="R21" t="n">
-        <v>6976237</v>
+        <v>6976524</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,49 +2847,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Eliasson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120336181</v>
+        <v>120336059</v>
       </c>
       <c r="B22" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,13 +2894,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450874</v>
+        <v>450821</v>
       </c>
       <c r="R22" t="n">
-        <v>6976230</v>
+        <v>6976771</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3088,6 +2930,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3114,37 +2961,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120336172</v>
+        <v>120336062</v>
       </c>
       <c r="B23" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3154,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450959</v>
+        <v>450866</v>
       </c>
       <c r="R23" t="n">
-        <v>6976237</v>
+        <v>6976496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3190,6 +3032,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,37 +3063,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120336058</v>
+        <v>120336064</v>
       </c>
       <c r="B24" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3256,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450840</v>
+        <v>450930</v>
       </c>
       <c r="R24" t="n">
-        <v>6976766</v>
+        <v>6976470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,37 +3165,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120336052</v>
+        <v>120336065</v>
       </c>
       <c r="B25" t="n">
-        <v>82348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450710</v>
+        <v>450976</v>
       </c>
       <c r="R25" t="n">
-        <v>6976591</v>
+        <v>6976536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,37 +3267,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120336061</v>
+        <v>120336176</v>
       </c>
       <c r="B26" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3470,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450820</v>
+        <v>450917</v>
       </c>
       <c r="R26" t="n">
-        <v>6976610</v>
+        <v>6976181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,11 +3338,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,15 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120336060</v>
+        <v>120193923</v>
       </c>
       <c r="B27" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3553,37 +3375,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450791</v>
+        <v>450990</v>
       </c>
       <c r="R27" t="n">
-        <v>6976761</v>
+        <v>6975968</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3607,17 +3438,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,6 +3454,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3644,15 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120336054</v>
+        <v>120193961</v>
       </c>
       <c r="B28" t="n">
-        <v>78646</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,37 +3506,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Östra Skrucksorkatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450821</v>
+        <v>451013</v>
       </c>
       <c r="R28" t="n">
-        <v>6976791</v>
+        <v>6976185</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,17 +3569,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,6 +3585,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3751,15 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120336063</v>
+        <v>120336051</v>
       </c>
       <c r="B29" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,21 +3637,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3791,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450895</v>
+        <v>450701</v>
       </c>
       <c r="R29" t="n">
-        <v>6976431</v>
+        <v>6976531</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,37 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120336640</v>
+        <v>120336056</v>
       </c>
       <c r="B30" t="n">
-        <v>87977</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3898,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450821</v>
+        <v>450831</v>
       </c>
       <c r="R30" t="n">
-        <v>6976791</v>
+        <v>6976781</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,6 +3799,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,15 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120336056</v>
+        <v>120336055</v>
       </c>
       <c r="B31" t="n">
-        <v>79674</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,21 +3841,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4000,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450831</v>
+        <v>450841</v>
       </c>
       <c r="R31" t="n">
-        <v>6976781</v>
+        <v>6976771</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4067,15 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120336062</v>
+        <v>120336181</v>
       </c>
       <c r="B32" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,21 +3943,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,13 +3967,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450866</v>
+        <v>450874</v>
       </c>
       <c r="R32" t="n">
-        <v>6976496</v>
+        <v>6976230</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,11 +4003,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,15 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120336051</v>
+        <v>120336184</v>
       </c>
       <c r="B33" t="n">
-        <v>78300</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4190,21 +4040,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,13 +4064,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450701</v>
+        <v>450866</v>
       </c>
       <c r="R33" t="n">
-        <v>6976531</v>
+        <v>6976252</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4250,11 +4100,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,15 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120336064</v>
+        <v>120336053</v>
       </c>
       <c r="B34" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,21 +4137,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4161,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450930</v>
+        <v>450750</v>
       </c>
       <c r="R34" t="n">
-        <v>6976470</v>
+        <v>6976700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4385,429 +4225,6 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>120336059</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>450821</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6976771</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>120336065</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>450976</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6976536</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120336184</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>450866</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6976252</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>120336053</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57446</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Östra Skrucksorkatjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>450750</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6976700</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Johan Eliasson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33400-2024 artfynd.xlsx
+++ b/artfynd/A 33400-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193947</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336172</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336054</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193942</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222152</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,6 +1989,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336058</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336063</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2162,6 +2232,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193901</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336052</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222146</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193883</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193913</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193935</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2856,6 +2956,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222157</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,6 +3063,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336059</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3060,6 +3170,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336062</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3162,6 +3277,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336064</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336065</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3361,6 +3486,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336176</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3492,6 +3622,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193923</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3623,6 +3758,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120193961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3725,6 +3865,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336051</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3827,6 +3972,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336056</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3929,6 +4079,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336055</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4026,6 +4181,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336181</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4123,6 +4283,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336184</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4225,8 +4390,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120336053</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>